--- a/Chernetsov_Geographical_pattern/R_calc_Chernetsov_Geographic_pattern/Data/Species_polygon_revision.xlsx
+++ b/Chernetsov_Geographical_pattern/R_calc_Chernetsov_Geographic_pattern/Data/Species_polygon_revision.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9264"/>
+    <workbookView windowWidth="22188" windowHeight="9324"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -1293,7 +1293,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1373,7 +1373,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
